--- a/output/reports/cv_experiment_all_models_qcut.xlsx
+++ b/output/reports/cv_experiment_all_models_qcut.xlsx
@@ -484,30 +484,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.635835886001587</v>
+        <v>17.44882559776306</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962548380768484</v>
+        <v>0.999988388422108</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9999905191874167</v>
       </c>
       <c r="G2" t="n">
-        <v>8.956775966344631</v>
+        <v>0.5479177221576782</v>
       </c>
       <c r="H2" t="n">
-        <v>5.924799097085533</v>
+        <v>0.04730246864744439</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -519,30 +519,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.671211957931519</v>
+        <v>29.74483442306519</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9970077248654106</v>
+        <v>0.9999911915977645</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9999905232810122</v>
       </c>
       <c r="G3" t="n">
-        <v>8.956775966344631</v>
+        <v>0.5477994202862353</v>
       </c>
       <c r="H3" t="n">
-        <v>5.924799097085533</v>
+        <v>0.04703679656408302</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -554,30 +554,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>3.043547630310059</v>
+        <v>61.93914127349854</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9973717366034205</v>
+        <v>0.9999921141350498</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9999905232810122</v>
       </c>
       <c r="G4" t="n">
-        <v>8.956775966344631</v>
+        <v>0.5477994202862353</v>
       </c>
       <c r="H4" t="n">
-        <v>5.924799097085533</v>
+        <v>0.04703679656408302</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -589,30 +589,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>3.063344240188599</v>
+        <v>94.08967304229736</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9974269041414209</v>
+        <v>0.9999925725862496</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9999905232810122</v>
       </c>
       <c r="G5" t="n">
-        <v>8.956775966344631</v>
+        <v>0.5477994202862353</v>
       </c>
       <c r="H5" t="n">
-        <v>5.924799097085533</v>
+        <v>0.04703679656408302</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -685,30 +685,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.635835886001587</v>
+        <v>17.44882559776306</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962548380768484</v>
+        <v>0.999988388422108</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9999905191874167</v>
       </c>
       <c r="G2" t="n">
-        <v>8.956775966344631</v>
+        <v>0.5479177221576782</v>
       </c>
       <c r="H2" t="n">
-        <v>5.924799097085533</v>
+        <v>0.04730246864744439</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -720,30 +720,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.671211957931519</v>
+        <v>29.74483442306519</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9970077248654106</v>
+        <v>0.9999911915977645</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9999905232810122</v>
       </c>
       <c r="G3" t="n">
-        <v>8.956775966344631</v>
+        <v>0.5477994202862353</v>
       </c>
       <c r="H3" t="n">
-        <v>5.924799097085533</v>
+        <v>0.04703679656408302</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -755,30 +755,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>3.043547630310059</v>
+        <v>61.93914127349854</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9973717366034205</v>
+        <v>0.9999921141350498</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9999905232810122</v>
       </c>
       <c r="G4" t="n">
-        <v>8.956775966344631</v>
+        <v>0.5477994202862353</v>
       </c>
       <c r="H4" t="n">
-        <v>5.924799097085533</v>
+        <v>0.04703679656408302</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -790,30 +790,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>3.063344240188599</v>
+        <v>94.08967304229736</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9974269041414209</v>
+        <v>0.9999925725862496</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9999905232810122</v>
       </c>
       <c r="G5" t="n">
-        <v>8.956775966344631</v>
+        <v>0.5477994202862353</v>
       </c>
       <c r="H5" t="n">
-        <v>5.924799097085533</v>
+        <v>0.04703679656408302</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_all_models_qcut.xlsx
+++ b/output/reports/cv_experiment_all_models_qcut.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>17.44882559776306</v>
+        <v>17.64760327339172</v>
       </c>
       <c r="E2" t="n">
         <v>0.999988388422108</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>29.74483442306519</v>
+        <v>30.73723268508911</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999911915977645</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>61.93914127349854</v>
+        <v>61.86629223823547</v>
       </c>
       <c r="E4" t="n">
         <v>0.9999921141350498</v>
@@ -596,7 +596,7 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>94.08967304229736</v>
+        <v>96.10405707359314</v>
       </c>
       <c r="E5" t="n">
         <v>0.9999925725862496</v>
@@ -613,6 +613,1546 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.601670265197754</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9998197420785205</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9998082929272684</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.463835082580447</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.380322209436134</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13.05957293510437</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9998312293752214</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9998082929272684</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.463835082580447</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.380322209436134</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16.14639353752136</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9998324116003632</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9998082929272684</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.463835082580447</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.380322209436134</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>22.16533970832825</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9998233887052492</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9998082929272684</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.463835082580447</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.380322209436134</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>26.32633185386658</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9998932697326653</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.99994714155579</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.29374818976295</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6823112120831791</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>38.44898915290833</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9999198365548818</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.99994714155579</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.29374818976295</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6823112120831791</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>74.73320746421814</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9999343494990329</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.99994714155579</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.29374818976295</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6823112120831791</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" t="n">
+        <v>112.6018803119659</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9999384639869466</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.99994714155579</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.29374818976295</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6823112120831791</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.354344606399536</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9962548380768484</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9974665152819624</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.956775966344631</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.924799097085533</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.570496082305908</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9970077248654106</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9974665152819624</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8.956775966344631</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.924799097085533</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.916466474533081</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9973717366034205</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9974665152819624</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8.956775966344631</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.924799097085533</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.253458976745605</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9974269041414209</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9974665152819624</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.956775966344631</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.924799097085533</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3199372291564941</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.815874837237964e-12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.546447319119009e-12</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.328242301940918</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.815874837237964e-12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.546447319119009e-12</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5251638889312744</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.815874837237964e-12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.546447319119009e-12</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.7051148414611816</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.815874837237964e-12</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.546447319119009e-12</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.15874195098877</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9999999999352088</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9999999999310575</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.001477528888338522</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.001275448318657181</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.153416633605957</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9999999999537585</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9999999999310575</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.001477528888338522</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.001275448318657181</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.41019344329834</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9999999999430331</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9999999999310575</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.001477528888338522</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.001275448318657181</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.872075796127319</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9999999999596234</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9999999999310575</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.001477528888338522</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.001275448318657181</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.845177173614502</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9999999999905905</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9999999999909073</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.000536586718073946</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0004225107608468285</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'l1_ratio': 0.1, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.058753252029419</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9999999999906969</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9999999999909073</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.000536586718073946</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0004225107608468285</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'l1_ratio': 0.1, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.679651975631714</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9999999999907973</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.9999999999909073</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.000536586718073946</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0004225107608468285</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'l1_ratio': 0.1, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.369414806365967</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9999999999907183</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9999999999909073</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.000536586718073946</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.0004225107608468285</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'l1_ratio': 0.1, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>12.24440121650696</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9999981778778437</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.9999995297855595</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1220226768832674</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.01586118393063176</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>20.11608862876892</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.999998942474002</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.9999995297855595</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1220226768832674</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.01586118393063176</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" t="n">
+        <v>39.82155513763428</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9999989736746795</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9999995297855595</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1220226768832674</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.01586118393063176</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>15</v>
+      </c>
+      <c r="D33" t="n">
+        <v>58.10947632789612</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.999999029190494</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9999995297855595</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1220226768832674</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.01586118393063176</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.721395015716553</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.999719520409902</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9997619986534119</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.74530553817749</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.336347937583923</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.320969104766846</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9997135281562806</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.9997619986534119</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.74530553817749</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.336347937583923</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.632920503616333</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9997214376926422</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9997619986534119</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.74530553817749</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.336347937583923</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>15</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.948121786117554</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9997140924135844</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9997619986534119</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.74530553817749</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.336347937583923</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4.550454139709473</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9998465119705559</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9998732856142044</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.003113363857107</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.6792505655304308</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3.293855667114258</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9998488094608649</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.9998732856142044</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.003113363857107</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6792505655304308</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7.8917076587677</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9999078901707481</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.9998732856142044</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.003113363857107</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6792505655304308</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>15</v>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4690101146698</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9999125459124918</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.9998732856142044</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.003113363857107</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6792505655304308</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>6.274673461914062</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9999952989031139</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.9999980186895508</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.2504775645776107</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.02845799769850308</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>11.89019393920898</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9999976282896125</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.9999980186895508</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.2504775645776107</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.02845799769850308</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" t="n">
+        <v>25.70109081268311</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9999979939925131</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.999997797671765</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.264078831902803</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.0301841196777909</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 25, 'max_samples': 1.0, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>15</v>
+      </c>
+      <c r="D45" t="n">
+        <v>39.7575249671936</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9999979563094777</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.9999980186895508</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.2504775645776107</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.02845799769850308</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>26.63461375236511</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9999999999989381</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.9999999999980579</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0002479899541464002</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.0001843707740354632</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>41.420814037323</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9999999999944957</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.9999999999980579</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0002479899541464002</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.0001843707740354632</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" t="n">
+        <v>81.46107649803162</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9999999999930822</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.9999999999980579</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0002479899541464002</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.0001843707740354632</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>15</v>
+      </c>
+      <c r="D49" t="n">
+        <v>115.8153793811798</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9999999999848707</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.9999999999993684</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.0001414200199542172</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.0001126384883517061</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -627,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,7 +2232,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>17.44882559776306</v>
+        <v>17.64760327339172</v>
       </c>
       <c r="E2" t="n">
         <v>0.999988388422108</v>
@@ -727,7 +2267,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>29.74483442306519</v>
+        <v>30.73723268508911</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999911915977645</v>
@@ -762,7 +2302,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>61.93914127349854</v>
+        <v>61.86629223823547</v>
       </c>
       <c r="E4" t="n">
         <v>0.9999921141350498</v>
@@ -797,7 +2337,7 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>94.08967304229736</v>
+        <v>96.10405707359314</v>
       </c>
       <c r="E5" t="n">
         <v>0.9999925725862496</v>
@@ -814,6 +2354,1546 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.601670265197754</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9998197420785205</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9998082929272684</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.463835082580447</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.380322209436134</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13.05957293510437</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9998312293752214</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9998082929272684</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.463835082580447</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.380322209436134</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16.14639353752136</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9998324116003632</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9998082929272684</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.463835082580447</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.380322209436134</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>22.16533970832825</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9998233887052492</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9998082929272684</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.463835082580447</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.380322209436134</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>26.32633185386658</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9998932697326653</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.99994714155579</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.29374818976295</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6823112120831791</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>38.44898915290833</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9999198365548818</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.99994714155579</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.29374818976295</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6823112120831791</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>74.73320746421814</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9999343494990329</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.99994714155579</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.29374818976295</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6823112120831791</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" t="n">
+        <v>112.6018803119659</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9999384639869466</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.99994714155579</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.29374818976295</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6823112120831791</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.354344606399536</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9962548380768484</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9974665152819624</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.956775966344631</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.924799097085533</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.570496082305908</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9970077248654106</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9974665152819624</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8.956775966344631</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.924799097085533</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.916466474533081</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9973717366034205</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9974665152819624</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8.956775966344631</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.924799097085533</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.253458976745605</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9974269041414209</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9974665152819624</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.956775966344631</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.924799097085533</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3199372291564941</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.815874837237964e-12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.546447319119009e-12</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.328242301940918</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.815874837237964e-12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.546447319119009e-12</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5251638889312744</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.815874837237964e-12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.546447319119009e-12</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.7051148414611816</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.815874837237964e-12</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.546447319119009e-12</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.15874195098877</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9999999999352088</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9999999999310575</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.001477528888338522</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.001275448318657181</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.153416633605957</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9999999999537585</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9999999999310575</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.001477528888338522</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.001275448318657181</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.41019344329834</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9999999999430331</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9999999999310575</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.001477528888338522</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.001275448318657181</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.872075796127319</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9999999999596234</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9999999999310575</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.001477528888338522</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.001275448318657181</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.845177173614502</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9999999999905905</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9999999999909073</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.000536586718073946</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0004225107608468285</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'l1_ratio': 0.1, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.058753252029419</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9999999999906969</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9999999999909073</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.000536586718073946</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0004225107608468285</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'l1_ratio': 0.1, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.679651975631714</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9999999999907973</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.9999999999909073</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.000536586718073946</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0004225107608468285</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'l1_ratio': 0.1, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.369414806365967</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9999999999907183</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9999999999909073</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.000536586718073946</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.0004225107608468285</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'selection': 'cyclic', 'l1_ratio': 0.1, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>12.24440121650696</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9999981778778437</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.9999995297855595</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1220226768832674</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.01586118393063176</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>20.11608862876892</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.999998942474002</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.9999995297855595</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1220226768832674</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.01586118393063176</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" t="n">
+        <v>39.82155513763428</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9999989736746795</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9999995297855595</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1220226768832674</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.01586118393063176</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>15</v>
+      </c>
+      <c r="D33" t="n">
+        <v>58.10947632789612</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.999999029190494</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9999995297855595</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1220226768832674</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.01586118393063176</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.721395015716553</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.999719520409902</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9997619986534119</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.74530553817749</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.336347937583923</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.320969104766846</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9997135281562806</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.9997619986534119</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.74530553817749</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.336347937583923</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.632920503616333</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9997214376926422</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9997619986534119</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.74530553817749</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.336347937583923</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>15</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.948121786117554</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9997140924135844</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9997619986534119</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.74530553817749</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.336347937583923</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4.550454139709473</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9998465119705559</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9998732856142044</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.003113363857107</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.6792505655304308</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3.293855667114258</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9998488094608649</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.9998732856142044</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.003113363857107</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6792505655304308</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7.8917076587677</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9999078901707481</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.9998732856142044</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.003113363857107</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6792505655304308</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>15</v>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4690101146698</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9999125459124918</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.9998732856142044</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.003113363857107</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6792505655304308</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>6.274673461914062</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9999952989031139</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.9999980186895508</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.2504775645776107</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.02845799769850308</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>11.89019393920898</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9999976282896125</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.9999980186895508</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.2504775645776107</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.02845799769850308</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" t="n">
+        <v>25.70109081268311</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9999979939925131</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.999997797671765</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.264078831902803</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.0301841196777909</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 25, 'max_samples': 1.0, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>15</v>
+      </c>
+      <c r="D45" t="n">
+        <v>39.7575249671936</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9999979563094777</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.9999980186895508</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.2504775645776107</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.02845799769850308</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>26.63461375236511</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9999999999989381</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.9999999999980579</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0002479899541464002</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.0001843707740354632</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>41.420814037323</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9999999999944957</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.9999999999980579</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0002479899541464002</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.0001843707740354632</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" t="n">
+        <v>81.46107649803162</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9999999999930822</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.9999999999980579</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0002479899541464002</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.0001843707740354632</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>15</v>
+      </c>
+      <c r="D49" t="n">
+        <v>115.8153793811798</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9999999999848707</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.9999999999993684</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.0001414200199542172</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.0001126384883517061</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_all_models_qcut.xlsx
+++ b/output/reports/cv_experiment_all_models_qcut.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,17 +457,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_R2</t>
+          <t>Test_Accuracy</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_RMSE</t>
+          <t>Test_F1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_MAE</t>
+          <t>Test_AUC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,30 +491,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.308979749679565</v>
+        <v>28.96171975135803</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9904659087366614</v>
+        <v>0.884370648297461</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9914582131506589</v>
+        <v>0.899417278946035</v>
       </c>
       <c r="G2" t="n">
-        <v>1.821308353709625</v>
+        <v>0.8986830586723202</v>
       </c>
       <c r="H2" t="n">
-        <v>1.215554266843641</v>
+        <v>0.961681313514882</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,30 +526,30 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.475330591201782</v>
+        <v>50.91848659515381</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9909618791532709</v>
+        <v>0.8897925336193475</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9914582131506589</v>
+        <v>0.8989105649860654</v>
       </c>
       <c r="G3" t="n">
-        <v>1.821308353709625</v>
+        <v>0.898207607994842</v>
       </c>
       <c r="H3" t="n">
-        <v>1.215554266843641</v>
+        <v>0.9609949523912853</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,30 +561,30 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1527729034423828</v>
+        <v>1.057622671127319</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9884016004359877</v>
+        <v>0.830471764728422</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.8538130225487712</v>
       </c>
       <c r="G4" t="n">
-        <v>1.908331770496365</v>
+        <v>0.8524453382050456</v>
       </c>
       <c r="H4" t="n">
-        <v>1.312303784373733</v>
+        <v>0.8879177709925241</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,100 +596,100 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1110231876373291</v>
+        <v>1.685253381729126</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9891276364518466</v>
+        <v>0.8404319695107754</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.8538130225487712</v>
       </c>
       <c r="G5" t="n">
-        <v>1.908331770496365</v>
+        <v>0.8524453382050456</v>
       </c>
       <c r="H5" t="n">
-        <v>1.312303784373733</v>
+        <v>0.8879177709925241</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1.295900821685791</v>
+        <v>855.2856223583221</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9907215425595718</v>
+        <v>0.8780279696355544</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.8844692171269318</v>
       </c>
       <c r="G6" t="n">
-        <v>1.541436429431279</v>
+        <v>0.8834054991099123</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9433131263880609</v>
+        <v>0.9502146654473876</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.534951448440552</v>
+        <v>1818.534924030304</v>
       </c>
       <c r="E7" t="n">
-        <v>0.994952709138001</v>
+        <v>0.8846320489711111</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.8844692171269318</v>
       </c>
       <c r="G7" t="n">
-        <v>1.541436429431279</v>
+        <v>0.8834054991099123</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9433131263880609</v>
+        <v>0.9502146654473876</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,30 +701,30 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.211597204208374</v>
+        <v>4.643058776855469</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9500806472555414</v>
+        <v>0.8817259419285336</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.893083354446415</v>
       </c>
       <c r="G8" t="n">
-        <v>4.117597323689839</v>
+        <v>0.892181422544394</v>
       </c>
       <c r="H8" t="n">
-        <v>3.150367965367966</v>
+        <v>0.9553259504952031</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,583 +736,303 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.100106954574585</v>
+        <v>5.089538812637329</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9586722896604414</v>
+        <v>0.8868223809415141</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.8915632125665062</v>
       </c>
       <c r="G9" t="n">
-        <v>4.117597323689839</v>
+        <v>0.8905966180796685</v>
       </c>
       <c r="H9" t="n">
-        <v>3.150367965367966</v>
+        <v>0.9587230118259739</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1782455444335938</v>
+        <v>1.401436567306519</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9095295397201048</v>
+        <v>0.7652244475735372</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9134071819812636</v>
+        <v>0.7686850772738789</v>
       </c>
       <c r="G10" t="n">
-        <v>5.798959174155399</v>
+        <v>0.7677078847255507</v>
       </c>
       <c r="H10" t="n">
-        <v>4.192639414719826</v>
+        <v>0.8423087255950443</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'alpha': 1e-05}</t>
+          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2461557388305664</v>
+        <v>2.315376043319702</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9087497339209655</v>
+        <v>0.7652393505542003</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9134071819812641</v>
+        <v>0.7684317202938941</v>
       </c>
       <c r="G11" t="n">
-        <v>5.79895917415538</v>
+        <v>0.7674457672264638</v>
       </c>
       <c r="H11" t="n">
-        <v>4.192639414719824</v>
+        <v>0.8422924513192496</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08743596076965332</v>
+        <v>0.2046976089477539</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9095325244128653</v>
+        <v>0.6586547164209363</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.665315429440081</v>
       </c>
       <c r="G12" t="n">
-        <v>5.798964155976802</v>
+        <v>0.6616285932988146</v>
       </c>
       <c r="H12" t="n">
-        <v>4.192993498939789</v>
+        <v>0.7263648434311339</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'selection': 'random', 'alpha': 1e-05}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05969381332397461</v>
+        <v>0.2610921859741211</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9087532778197251</v>
+        <v>0.6590294599111231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.665315429440081</v>
       </c>
       <c r="G13" t="n">
-        <v>5.798964155976802</v>
+        <v>0.6616285932988146</v>
       </c>
       <c r="H13" t="n">
-        <v>4.192993498939789</v>
+        <v>0.7263653600748099</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'selection': 'random', 'alpha': 1e-05}</t>
+          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.194368839263916</v>
+        <v>37.76048135757446</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9095325244128653</v>
+        <v>0.8825712016553097</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.8978971370661262</v>
       </c>
       <c r="G14" t="n">
-        <v>5.798964155976802</v>
+        <v>0.897097208156062</v>
       </c>
       <c r="H14" t="n">
-        <v>4.192993498939789</v>
+        <v>0.9600591815330886</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'selection': 'random', 'l1_ratio': 1.0, 'alpha': 1e-05}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1368212699890137</v>
+        <v>73.87733936309814</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9087558070992785</v>
+        <v>0.8872486501526529</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9133757607379048</v>
+        <v>0.8978971370661262</v>
       </c>
       <c r="G15" t="n">
-        <v>5.800011189699457</v>
+        <v>0.897097208156062</v>
       </c>
       <c r="H15" t="n">
-        <v>4.193244794799755</v>
+        <v>0.9600591815330886</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'selection': 'cyclic', 'l1_ratio': 0.7, 'alpha': 1e-05}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7141377925872803</v>
+        <v>147.3877637386322</v>
       </c>
       <c r="E16" t="n">
-        <v>0.996280288687481</v>
+        <v>0.8848774569771193</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9978246390639918</v>
+        <v>0.8973904231061566</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9191254197681974</v>
+        <v>0.8966414074616869</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6382677938619158</v>
+        <v>0.9621199439958255</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.151675224304199</v>
+        <v>202.4163522720337</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9975377648378924</v>
+        <v>0.8898315700176177</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9978362843422668</v>
+        <v>0.896883709146187</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9166619586020609</v>
+        <v>0.8961309946590286</v>
       </c>
       <c r="H17" t="n">
-        <v>0.581795188945029</v>
+        <v>0.9622568545699719</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.832290172576904</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.9965068384805602</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.9981012350213448</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.8587064421248826</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5801936221432377</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 3, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.5191829204559326</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.9973711609502469</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.9981012350213448</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.8587064421248826</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5801936221432377</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 3, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4.806221485137939</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.9951408832698706</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.9972029819630599</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.042213628938737</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.7334044627491686</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.944318532943726</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.99609907442234</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.9972029819630599</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.042213628938737</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.7334044627491686</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.399111270904541</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.9916308390247451</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.9922108407265826</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.739219543134441</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.121023376623376</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.957748651504517</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.991944820007945</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9924359336701404</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.713905130730069</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.105564935064935</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.186573266983032</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.9919591707630674</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.9931963895337861</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.625469537425023</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.102047839255723</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.433193683624268</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.9922542316820335</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.9931963895337861</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.625469537425023</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.102047839255723</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1358,17 +1078,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_R2</t>
+          <t>Test_Accuracy</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_RMSE</t>
+          <t>Test_F1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_MAE</t>
+          <t>Test_AUC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1380,7 +1100,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1392,30 +1112,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.308979749679565</v>
+        <v>28.96171975135803</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9904659087366614</v>
+        <v>0.884370648297461</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9914582131506589</v>
+        <v>0.899417278946035</v>
       </c>
       <c r="G2" t="n">
-        <v>1.821308353709625</v>
+        <v>0.8986830586723202</v>
       </c>
       <c r="H2" t="n">
-        <v>1.215554266843641</v>
+        <v>0.961681313514882</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1427,30 +1147,30 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.475330591201782</v>
+        <v>50.91848659515381</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9909618791532709</v>
+        <v>0.8897925336193475</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9914582131506589</v>
+        <v>0.8989105649860654</v>
       </c>
       <c r="G3" t="n">
-        <v>1.821308353709625</v>
+        <v>0.898207607994842</v>
       </c>
       <c r="H3" t="n">
-        <v>1.215554266843641</v>
+        <v>0.9609949523912853</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1462,30 +1182,30 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1527729034423828</v>
+        <v>1.057622671127319</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9884016004359877</v>
+        <v>0.830471764728422</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.8538130225487712</v>
       </c>
       <c r="G4" t="n">
-        <v>1.908331770496365</v>
+        <v>0.8524453382050456</v>
       </c>
       <c r="H4" t="n">
-        <v>1.312303784373733</v>
+        <v>0.8879177709925241</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1497,100 +1217,100 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1110231876373291</v>
+        <v>1.685253381729126</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9891276364518466</v>
+        <v>0.8404319695107754</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.8538130225487712</v>
       </c>
       <c r="G5" t="n">
-        <v>1.908331770496365</v>
+        <v>0.8524453382050456</v>
       </c>
       <c r="H5" t="n">
-        <v>1.312303784373733</v>
+        <v>0.8879177709925241</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1.295900821685791</v>
+        <v>855.2856223583221</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9907215425595718</v>
+        <v>0.8780279696355544</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.8844692171269318</v>
       </c>
       <c r="G6" t="n">
-        <v>1.541436429431279</v>
+        <v>0.8834054991099123</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9433131263880609</v>
+        <v>0.9502146654473876</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.534951448440552</v>
+        <v>1818.534924030304</v>
       </c>
       <c r="E7" t="n">
-        <v>0.994952709138001</v>
+        <v>0.8846320489711111</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.8844692171269318</v>
       </c>
       <c r="G7" t="n">
-        <v>1.541436429431279</v>
+        <v>0.8834054991099123</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9433131263880609</v>
+        <v>0.9502146654473876</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1602,30 +1322,30 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.211597204208374</v>
+        <v>4.643058776855469</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9500806472555414</v>
+        <v>0.8817259419285336</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.893083354446415</v>
       </c>
       <c r="G8" t="n">
-        <v>4.117597323689839</v>
+        <v>0.892181422544394</v>
       </c>
       <c r="H8" t="n">
-        <v>3.150367965367966</v>
+        <v>0.9553259504952031</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1637,583 +1357,303 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.100106954574585</v>
+        <v>5.089538812637329</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9586722896604414</v>
+        <v>0.8868223809415141</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.8915632125665062</v>
       </c>
       <c r="G9" t="n">
-        <v>4.117597323689839</v>
+        <v>0.8905966180796685</v>
       </c>
       <c r="H9" t="n">
-        <v>3.150367965367966</v>
+        <v>0.9587230118259739</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1782455444335938</v>
+        <v>1.401436567306519</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9095295397201048</v>
+        <v>0.7652244475735372</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9134071819812636</v>
+        <v>0.7686850772738789</v>
       </c>
       <c r="G10" t="n">
-        <v>5.798959174155399</v>
+        <v>0.7677078847255507</v>
       </c>
       <c r="H10" t="n">
-        <v>4.192639414719826</v>
+        <v>0.8423087255950443</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'alpha': 1e-05}</t>
+          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2461557388305664</v>
+        <v>2.315376043319702</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9087497339209655</v>
+        <v>0.7652393505542003</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9134071819812641</v>
+        <v>0.7684317202938941</v>
       </c>
       <c r="G11" t="n">
-        <v>5.79895917415538</v>
+        <v>0.7674457672264638</v>
       </c>
       <c r="H11" t="n">
-        <v>4.192639414719824</v>
+        <v>0.8422924513192496</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08743596076965332</v>
+        <v>0.2046976089477539</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9095325244128653</v>
+        <v>0.6586547164209363</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.665315429440081</v>
       </c>
       <c r="G12" t="n">
-        <v>5.798964155976802</v>
+        <v>0.6616285932988146</v>
       </c>
       <c r="H12" t="n">
-        <v>4.192993498939789</v>
+        <v>0.7263648434311339</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'selection': 'random', 'alpha': 1e-05}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05969381332397461</v>
+        <v>0.2610921859741211</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9087532778197251</v>
+        <v>0.6590294599111231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.665315429440081</v>
       </c>
       <c r="G13" t="n">
-        <v>5.798964155976802</v>
+        <v>0.6616285932988146</v>
       </c>
       <c r="H13" t="n">
-        <v>4.192993498939789</v>
+        <v>0.7263653600748099</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'selection': 'random', 'alpha': 1e-05}</t>
+          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.194368839263916</v>
+        <v>37.76048135757446</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9095325244128653</v>
+        <v>0.8825712016553097</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.8978971370661262</v>
       </c>
       <c r="G14" t="n">
-        <v>5.798964155976802</v>
+        <v>0.897097208156062</v>
       </c>
       <c r="H14" t="n">
-        <v>4.192993498939789</v>
+        <v>0.9600591815330886</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'selection': 'random', 'l1_ratio': 1.0, 'alpha': 1e-05}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1368212699890137</v>
+        <v>73.87733936309814</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9087558070992785</v>
+        <v>0.8872486501526529</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9133757607379048</v>
+        <v>0.8978971370661262</v>
       </c>
       <c r="G15" t="n">
-        <v>5.800011189699457</v>
+        <v>0.897097208156062</v>
       </c>
       <c r="H15" t="n">
-        <v>4.193244794799755</v>
+        <v>0.9600591815330886</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'selection': 'cyclic', 'l1_ratio': 0.7, 'alpha': 1e-05}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7141377925872803</v>
+        <v>147.3877637386322</v>
       </c>
       <c r="E16" t="n">
-        <v>0.996280288687481</v>
+        <v>0.8848774569771193</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9978246390639918</v>
+        <v>0.8973904231061566</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9191254197681974</v>
+        <v>0.8966414074616869</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6382677938619158</v>
+        <v>0.9621199439958255</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.151675224304199</v>
+        <v>202.4163522720337</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9975377648378924</v>
+        <v>0.8898315700176177</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9978362843422668</v>
+        <v>0.896883709146187</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9166619586020609</v>
+        <v>0.8961309946590286</v>
       </c>
       <c r="H17" t="n">
-        <v>0.581795188945029</v>
+        <v>0.9622568545699719</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.832290172576904</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.9965068384805602</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.9981012350213448</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.8587064421248826</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5801936221432377</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 3, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.5191829204559326</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.9973711609502469</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.9981012350213448</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.8587064421248826</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5801936221432377</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 3, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4.806221485137939</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.9951408832698706</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.9972029819630599</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.042213628938737</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.7334044627491686</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.944318532943726</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.99609907442234</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.9972029819630599</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.042213628938737</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.7334044627491686</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.399111270904541</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.9916308390247451</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.9922108407265826</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.739219543134441</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.121023376623376</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.957748651504517</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.991944820007945</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9924359336701404</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.713905130730069</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.105564935064935</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.186573266983032</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.9919591707630674</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.9931963895337861</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.625469537425023</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.102047839255723</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.433193683624268</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.9922542316820335</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.9931963895337861</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.625469537425023</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.102047839255723</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_all_models_qcut.xlsx
+++ b/output/reports/cv_experiment_all_models_qcut.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>28.96171975135803</v>
+        <v>2.144138813018799</v>
       </c>
       <c r="E2" t="n">
-        <v>0.884370648297461</v>
+        <v>0.9951175357102523</v>
       </c>
       <c r="F2" t="n">
-        <v>0.899417278946035</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8986830586723202</v>
+        <v>0.986933650093331</v>
       </c>
       <c r="H2" t="n">
-        <v>0.961681313514882</v>
+        <v>0.9994909214322077</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 6}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>50.91848659515381</v>
+        <v>1.117149114608765</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8897925336193475</v>
+        <v>0.9918502377727062</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8989105649860654</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.898207607994842</v>
+        <v>0.986933650093331</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9609949523912853</v>
+        <v>0.9994909214322077</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 6}</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.057622671127319</v>
+        <v>0.04854393005371094</v>
       </c>
       <c r="E4" t="n">
-        <v>0.830471764728422</v>
+        <v>0.9918638006855159</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8538130225487712</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8524453382050456</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8879177709925241</v>
+        <v>0.9796368572883082</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 7, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -596,23 +596,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.685253381729126</v>
+        <v>0.05994701385498047</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8404319695107754</v>
+        <v>0.9902363723372692</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8538130225487712</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8524453382050456</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8879177709925241</v>
+        <v>0.9796368572883082</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 7, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -631,19 +631,19 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>855.2856223583221</v>
+        <v>0.09575986862182617</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8780279696355544</v>
+        <v>0.9788327554767209</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8844692171269318</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8834054991099123</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9502146654473876</v>
+        <v>0.9977939928729</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -666,19 +666,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1818.534924030304</v>
+        <v>0.1598746776580811</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8846320489711111</v>
+        <v>0.9788200709583792</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8844692171269318</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8834054991099123</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9502146654473876</v>
+        <v>0.9977939928729</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -701,23 +701,23 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4.643058776855469</v>
+        <v>0.06891679763793945</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8817259419285336</v>
+        <v>0.9869704489949077</v>
       </c>
       <c r="F8" t="n">
-        <v>0.893083354446415</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G8" t="n">
-        <v>0.892181422544394</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9553259504952031</v>
+        <v>0.9929577464788731</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -736,23 +736,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5.089538812637329</v>
+        <v>0.06421852111816406</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8868223809415141</v>
+        <v>0.9837078852912551</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8915632125665062</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8905966180796685</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9587230118259739</v>
+        <v>0.9929577464788731</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -771,23 +771,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.401436567306519</v>
+        <v>0.1158936023712158</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7652244475735372</v>
+        <v>0.9788276918439337</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7686850772738789</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7677078847255507</v>
+        <v>0.9804195804195804</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8423087255950443</v>
+        <v>0.9791277787205159</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
+          <t>{'solver': 'lbfgs', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -806,23 +806,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.315376043319702</v>
+        <v>0.2169575691223145</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7652393505542003</v>
+        <v>0.9788177038381292</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7684317202938941</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7674457672264638</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8422924513192496</v>
+        <v>0.9986424571525538</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -841,19 +841,19 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2046976089477539</v>
+        <v>0.02727746963500977</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6586547164209363</v>
+        <v>0.9788276918439337</v>
       </c>
       <c r="F12" t="n">
-        <v>0.665315429440081</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6616285932988146</v>
+        <v>0.9804195804195804</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7263648434311339</v>
+        <v>0.9746309180383507</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -876,23 +876,23 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2610921859741211</v>
+        <v>0.04120945930480957</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6590294599111231</v>
+        <v>0.9788074876046238</v>
       </c>
       <c r="F13" t="n">
-        <v>0.665315429440081</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6616285932988146</v>
+        <v>0.9804195804195804</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7263653600748099</v>
+        <v>0.9746309180383507</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -911,23 +911,23 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>37.76048135757446</v>
+        <v>0.8247137069702148</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8825712016553097</v>
+        <v>0.9951186213925265</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8978971370661262</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G14" t="n">
-        <v>0.897097208156062</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9600591815330886</v>
+        <v>0.9994909214322077</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 25, 'max_samples': 0.8, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -946,23 +946,23 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>73.87733936309814</v>
+        <v>1.429044008255005</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8872486501526529</v>
+        <v>0.991859371617992</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8978971370661262</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G15" t="n">
-        <v>0.897097208156062</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9600591815330886</v>
+        <v>0.9989818428644154</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -981,19 +981,19 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>147.3877637386322</v>
+        <v>1.09474515914917</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8848774569771193</v>
+        <v>0.9934911333772632</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8973904231061566</v>
+        <v>0.9675324675324676</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8966414074616869</v>
+        <v>0.9672994436658597</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9621199439958255</v>
+        <v>0.9986424571525538</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1016,19 +1016,19 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>202.4163522720337</v>
+        <v>0.9859244823455811</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8898315700176177</v>
+        <v>0.9934903405912376</v>
       </c>
       <c r="F17" t="n">
-        <v>0.896883709146187</v>
+        <v>0.9675324675324676</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8961309946590286</v>
+        <v>0.9672994436658597</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9622568545699719</v>
+        <v>0.9986424571525538</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1112,23 +1112,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>28.96171975135803</v>
+        <v>2.144138813018799</v>
       </c>
       <c r="E2" t="n">
-        <v>0.884370648297461</v>
+        <v>0.9951175357102523</v>
       </c>
       <c r="F2" t="n">
-        <v>0.899417278946035</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8986830586723202</v>
+        <v>0.986933650093331</v>
       </c>
       <c r="H2" t="n">
-        <v>0.961681313514882</v>
+        <v>0.9994909214322077</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 6}</t>
         </is>
       </c>
     </row>
@@ -1147,23 +1147,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>50.91848659515381</v>
+        <v>1.117149114608765</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8897925336193475</v>
+        <v>0.9918502377727062</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8989105649860654</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.898207607994842</v>
+        <v>0.986933650093331</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9609949523912853</v>
+        <v>0.9994909214322077</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 6}</t>
         </is>
       </c>
     </row>
@@ -1182,23 +1182,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.057622671127319</v>
+        <v>0.04854393005371094</v>
       </c>
       <c r="E4" t="n">
-        <v>0.830471764728422</v>
+        <v>0.9918638006855159</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8538130225487712</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8524453382050456</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8879177709925241</v>
+        <v>0.9796368572883082</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 7, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -1217,23 +1217,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.685253381729126</v>
+        <v>0.05994701385498047</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8404319695107754</v>
+        <v>0.9902363723372692</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8538130225487712</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8524453382050456</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8879177709925241</v>
+        <v>0.9796368572883082</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 7, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -1252,19 +1252,19 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>855.2856223583221</v>
+        <v>0.09575986862182617</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8780279696355544</v>
+        <v>0.9788327554767209</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8844692171269318</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8834054991099123</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9502146654473876</v>
+        <v>0.9977939928729</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1287,19 +1287,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1818.534924030304</v>
+        <v>0.1598746776580811</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8846320489711111</v>
+        <v>0.9788200709583792</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8844692171269318</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8834054991099123</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9502146654473876</v>
+        <v>0.9977939928729</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1322,23 +1322,23 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4.643058776855469</v>
+        <v>0.06891679763793945</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8817259419285336</v>
+        <v>0.9869704489949077</v>
       </c>
       <c r="F8" t="n">
-        <v>0.893083354446415</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G8" t="n">
-        <v>0.892181422544394</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9553259504952031</v>
+        <v>0.9929577464788731</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -1357,23 +1357,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5.089538812637329</v>
+        <v>0.06421852111816406</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8868223809415141</v>
+        <v>0.9837078852912551</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8915632125665062</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8905966180796685</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9587230118259739</v>
+        <v>0.9929577464788731</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -1392,23 +1392,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.401436567306519</v>
+        <v>0.1158936023712158</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7652244475735372</v>
+        <v>0.9788276918439337</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7686850772738789</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7677078847255507</v>
+        <v>0.9804195804195804</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8423087255950443</v>
+        <v>0.9791277787205159</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
+          <t>{'solver': 'lbfgs', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -1427,23 +1427,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.315376043319702</v>
+        <v>0.2169575691223145</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7652393505542003</v>
+        <v>0.9788177038381292</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7684317202938941</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7674457672264638</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8422924513192496</v>
+        <v>0.9986424571525538</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -1462,19 +1462,19 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2046976089477539</v>
+        <v>0.02727746963500977</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6586547164209363</v>
+        <v>0.9788276918439337</v>
       </c>
       <c r="F12" t="n">
-        <v>0.665315429440081</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6616285932988146</v>
+        <v>0.9804195804195804</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7263648434311339</v>
+        <v>0.9746309180383507</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1497,23 +1497,23 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2610921859741211</v>
+        <v>0.04120945930480957</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6590294599111231</v>
+        <v>0.9788074876046238</v>
       </c>
       <c r="F13" t="n">
-        <v>0.665315429440081</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6616285932988146</v>
+        <v>0.9804195804195804</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7263653600748099</v>
+        <v>0.9746309180383507</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -1532,23 +1532,23 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>37.76048135757446</v>
+        <v>0.8247137069702148</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8825712016553097</v>
+        <v>0.9951186213925265</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8978971370661262</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G14" t="n">
-        <v>0.897097208156062</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9600591815330886</v>
+        <v>0.9994909214322077</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 25, 'max_samples': 0.8, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -1567,23 +1567,23 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>73.87733936309814</v>
+        <v>1.429044008255005</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8872486501526529</v>
+        <v>0.991859371617992</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8978971370661262</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G15" t="n">
-        <v>0.897097208156062</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9600591815330886</v>
+        <v>0.9989818428644154</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -1602,19 +1602,19 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>147.3877637386322</v>
+        <v>1.09474515914917</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8848774569771193</v>
+        <v>0.9934911333772632</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8973904231061566</v>
+        <v>0.9675324675324676</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8966414074616869</v>
+        <v>0.9672994436658597</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9621199439958255</v>
+        <v>0.9986424571525538</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>202.4163522720337</v>
+        <v>0.9859244823455811</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8898315700176177</v>
+        <v>0.9934903405912376</v>
       </c>
       <c r="F17" t="n">
-        <v>0.896883709146187</v>
+        <v>0.9675324675324676</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8961309946590286</v>
+        <v>0.9672994436658597</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9622568545699719</v>
+        <v>0.9986424571525538</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
